--- a/MR_UKBiobank/BinaryData/SA_Birth/gMR_res.xlsx
+++ b/MR_UKBiobank/BinaryData/SA_Birth/gMR_res.xlsx
@@ -135,28 +135,28 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.3657941859084055</v>
+        <v>-1.3198261799425832</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.6404566650240828</v>
+        <v>-1.5960433648474326</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.0911317067927282</v>
+        <v>-1.0436089950377339</v>
       </c>
       <c r="F2" t="n">
-        <v>0.14013391791616192</v>
+        <v>0.14092713515553543</v>
       </c>
       <c r="G2" t="n">
-        <v>1.912204594734816E-22</v>
+        <v>7.582802042001386E-21</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2551779367708997</v>
+        <v>0.26718173947514445</v>
       </c>
       <c r="I2" t="n">
-        <v>0.19389147861371353</v>
+        <v>0.20269693128240646</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3358362104421427</v>
+        <v>0.35218136484516227</v>
       </c>
     </row>
   </sheetData>
@@ -207,28 +207,28 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5821448812046267</v>
+        <v>0.5603103738924813</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4456055952492079</v>
+        <v>0.4281584206234528</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7186841671600455</v>
+        <v>0.6924623271615098</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06966290099766266</v>
+        <v>0.06742446595358598</v>
       </c>
       <c r="G2" t="n">
-        <v>6.455263607305305E-17</v>
+        <v>9.554596145322953E-17</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7898733822984492</v>
+        <v>1.7512159476660532</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5614355074909323</v>
+        <v>1.534429146935842</v>
       </c>
       <c r="J2" t="n">
-        <v>2.0517316977173294</v>
+        <v>1.9986307621202537</v>
       </c>
     </row>
   </sheetData>
@@ -279,28 +279,28 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5440212847626991</v>
+        <v>0.5182257460000596</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3621864547316229</v>
+        <v>0.32384806026798046</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7258561147937752</v>
+        <v>0.7126034317321386</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09277287246483476</v>
+        <v>0.09917228863881586</v>
       </c>
       <c r="G2" t="n">
-        <v>4.518134154701415E-9</v>
+        <v>1.7367611223103537E-7</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7229213075917942</v>
+        <v>1.67904595134071</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4364667530151756</v>
+        <v>1.382437244017028</v>
       </c>
       <c r="J2" t="n">
-        <v>2.0664995036766145</v>
+        <v>2.0392935150688873</v>
       </c>
     </row>
   </sheetData>
@@ -351,28 +351,28 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.14963254700179737</v>
+        <v>-0.14043945990236797</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.41797490772594814</v>
+        <v>-0.40018083022286965</v>
       </c>
       <c r="E2" t="n">
-        <v>0.11870981372235342</v>
+        <v>0.11930191041813368</v>
       </c>
       <c r="F2" t="n">
-        <v>0.13690936771640347</v>
+        <v>0.1325211073063784</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2744239202684682</v>
+        <v>0.2892576060076933</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8610243042658196</v>
+        <v>0.8689762712486659</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6583787484375496</v>
+        <v>0.6701988428712485</v>
       </c>
       <c r="J2" t="n">
-        <v>1.1260431086146465</v>
+        <v>1.1267100324407762</v>
       </c>
     </row>
   </sheetData>
@@ -423,28 +423,28 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001256794488496452</v>
+        <v>0.003878480276442189</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.06843409582139569</v>
+        <v>-0.06349978240120158</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0709476847983886</v>
+        <v>0.07125674295408596</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03555657668872048</v>
+        <v>0.0343766646314509</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9718035805028898</v>
+        <v>0.9101708409034004</v>
       </c>
       <c r="H2" t="n">
-        <v>1.0012575845856515</v>
+        <v>1.0038860113142491</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9338550030224425</v>
+        <v>0.9384743235115269</v>
       </c>
       <c r="J2" t="n">
-        <v>1.073525062719186</v>
+        <v>1.0738568956703634</v>
       </c>
     </row>
   </sheetData>
@@ -495,28 +495,28 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3886014068137135</v>
+        <v>0.3713318452006961</v>
       </c>
       <c r="D2" t="n">
-        <v>0.20365214618346125</v>
+        <v>0.18458369700340496</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5735506674439658</v>
+        <v>0.5580799933979873</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09436186766849605</v>
+        <v>0.09527966744759753</v>
       </c>
       <c r="G2" t="n">
-        <v>3.818368616903005E-5</v>
+        <v>9.72778484106058E-5</v>
       </c>
       <c r="H2" t="n">
-        <v>1.4749165424685073</v>
+        <v>1.4496640576362214</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2258716551471494</v>
+        <v>1.2027176409348468</v>
       </c>
       <c r="J2" t="n">
-        <v>1.7745567393726316</v>
+        <v>1.7473144223351067</v>
       </c>
     </row>
   </sheetData>

--- a/MR_UKBiobank/BinaryData/SA_Birth/gMR_res.xlsx
+++ b/MR_UKBiobank/BinaryData/SA_Birth/gMR_res.xlsx
@@ -135,28 +135,28 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.3198261799425832</v>
+        <v>-1.3657941859084055</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.5960433648474326</v>
+        <v>-1.6404566650240828</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.0436089950377339</v>
+        <v>-1.0911317067927282</v>
       </c>
       <c r="F2" t="n">
-        <v>0.14092713515553543</v>
+        <v>0.14013391791616192</v>
       </c>
       <c r="G2" t="n">
-        <v>7.582802042001386E-21</v>
+        <v>1.912204594734816E-22</v>
       </c>
       <c r="H2" t="n">
-        <v>0.26718173947514445</v>
+        <v>0.2551779367708997</v>
       </c>
       <c r="I2" t="n">
-        <v>0.20269693128240646</v>
+        <v>0.19389147861371353</v>
       </c>
       <c r="J2" t="n">
-        <v>0.35218136484516227</v>
+        <v>0.3358362104421427</v>
       </c>
     </row>
   </sheetData>
@@ -207,28 +207,28 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5603103738924813</v>
+        <v>0.5821448812046267</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4281584206234528</v>
+        <v>0.4456055952492079</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6924623271615098</v>
+        <v>0.7186841671600455</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06742446595358598</v>
+        <v>0.06966290099766266</v>
       </c>
       <c r="G2" t="n">
-        <v>9.554596145322953E-17</v>
+        <v>6.455263607305305E-17</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7512159476660532</v>
+        <v>1.7898733822984492</v>
       </c>
       <c r="I2" t="n">
-        <v>1.534429146935842</v>
+        <v>1.5614355074909323</v>
       </c>
       <c r="J2" t="n">
-        <v>1.9986307621202537</v>
+        <v>2.0517316977173294</v>
       </c>
     </row>
   </sheetData>
@@ -279,28 +279,28 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5182257460000596</v>
+        <v>0.5440212847626991</v>
       </c>
       <c r="D2" t="n">
-        <v>0.32384806026798046</v>
+        <v>0.3621864547316229</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7126034317321386</v>
+        <v>0.7258561147937752</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09917228863881586</v>
+        <v>0.09277287246483476</v>
       </c>
       <c r="G2" t="n">
-        <v>1.7367611223103537E-7</v>
+        <v>4.518134154701415E-9</v>
       </c>
       <c r="H2" t="n">
-        <v>1.67904595134071</v>
+        <v>1.7229213075917942</v>
       </c>
       <c r="I2" t="n">
-        <v>1.382437244017028</v>
+        <v>1.4364667530151756</v>
       </c>
       <c r="J2" t="n">
-        <v>2.0392935150688873</v>
+        <v>2.0664995036766145</v>
       </c>
     </row>
   </sheetData>
@@ -351,28 +351,28 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.14043945990236797</v>
+        <v>-0.14963254700179737</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.40018083022286965</v>
+        <v>-0.41797490772594814</v>
       </c>
       <c r="E2" t="n">
-        <v>0.11930191041813368</v>
+        <v>0.11870981372235342</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1325211073063784</v>
+        <v>0.13690936771640347</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2892576060076933</v>
+        <v>0.2744239202684682</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8689762712486659</v>
+        <v>0.8610243042658196</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6701988428712485</v>
+        <v>0.6583787484375496</v>
       </c>
       <c r="J2" t="n">
-        <v>1.1267100324407762</v>
+        <v>1.1260431086146465</v>
       </c>
     </row>
   </sheetData>
@@ -423,28 +423,28 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003878480276442189</v>
+        <v>0.001256794488496452</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.06349978240120158</v>
+        <v>-0.06843409582139569</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07125674295408596</v>
+        <v>0.0709476847983886</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0343766646314509</v>
+        <v>0.03555657668872048</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9101708409034004</v>
+        <v>0.9718035805028898</v>
       </c>
       <c r="H2" t="n">
-        <v>1.0038860113142491</v>
+        <v>1.0012575845856515</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9384743235115269</v>
+        <v>0.9338550030224425</v>
       </c>
       <c r="J2" t="n">
-        <v>1.0738568956703634</v>
+        <v>1.073525062719186</v>
       </c>
     </row>
   </sheetData>
@@ -495,28 +495,28 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3713318452006961</v>
+        <v>0.3886014068137135</v>
       </c>
       <c r="D2" t="n">
-        <v>0.18458369700340496</v>
+        <v>0.20365214618346125</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5580799933979873</v>
+        <v>0.5735506674439658</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09527966744759753</v>
+        <v>0.09436186766849605</v>
       </c>
       <c r="G2" t="n">
-        <v>9.72778484106058E-5</v>
+        <v>3.818368616903005E-5</v>
       </c>
       <c r="H2" t="n">
-        <v>1.4496640576362214</v>
+        <v>1.4749165424685073</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2027176409348468</v>
+        <v>1.2258716551471494</v>
       </c>
       <c r="J2" t="n">
-        <v>1.7473144223351067</v>
+        <v>1.7745567393726316</v>
       </c>
     </row>
   </sheetData>

--- a/MR_UKBiobank/BinaryData/SA_Birth/gMR_res.xlsx
+++ b/MR_UKBiobank/BinaryData/SA_Birth/gMR_res.xlsx
@@ -135,28 +135,28 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.3657941859084055</v>
+        <v>-1.224876707790928</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.6404566650240828</v>
+        <v>-1.3994469921544324</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.0911317067927282</v>
+        <v>-1.0503064234274235</v>
       </c>
       <c r="F2" t="n">
-        <v>0.14013391791616192</v>
+        <v>0.0890664716140329</v>
       </c>
       <c r="G2" t="n">
-        <v>1.912204594734816E-22</v>
+        <v>4.927555409729593E-43</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2551779367708997</v>
+        <v>0.2937939205921302</v>
       </c>
       <c r="I2" t="n">
-        <v>0.19389147861371353</v>
+        <v>0.2467333717111664</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3358362104421427</v>
+        <v>0.3498305364137678</v>
       </c>
     </row>
   </sheetData>
@@ -207,28 +207,28 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5821448812046267</v>
+        <v>0.551435607970794</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4456055952492079</v>
+        <v>0.39218482588671044</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7186841671600455</v>
+        <v>0.7106863900548777</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06966290099766266</v>
+        <v>0.08125039902249165</v>
       </c>
       <c r="G2" t="n">
-        <v>6.455263607305305E-17</v>
+        <v>1.145951868109022E-11</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7898733822984492</v>
+        <v>1.7357430766617135</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5614355074909323</v>
+        <v>1.4802112674814183</v>
       </c>
       <c r="J2" t="n">
-        <v>2.0517316977173294</v>
+        <v>2.0353878492665185</v>
       </c>
     </row>
   </sheetData>
@@ -279,28 +279,28 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5440212847626991</v>
+        <v>0.6378006480727967</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3621864547316229</v>
+        <v>0.3955406463753416</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7258561147937752</v>
+        <v>0.8800606497702518</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09277287246483476</v>
+        <v>0.12360204168237507</v>
       </c>
       <c r="G2" t="n">
-        <v>4.518134154701415E-9</v>
+        <v>2.467992754049873E-7</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7229213075917942</v>
+        <v>1.8923144338475473</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4364667530151756</v>
+        <v>1.4851869348340898</v>
       </c>
       <c r="J2" t="n">
-        <v>2.0664995036766145</v>
+        <v>2.411045931364714</v>
       </c>
     </row>
   </sheetData>
@@ -351,28 +351,28 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.14963254700179737</v>
+        <v>-0.029688823333450576</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.41797490772594814</v>
+        <v>-0.34450582377210565</v>
       </c>
       <c r="E2" t="n">
-        <v>0.11870981372235342</v>
+        <v>0.2851281771052045</v>
       </c>
       <c r="F2" t="n">
-        <v>0.13690936771640347</v>
+        <v>0.16062091859115055</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2744239202684682</v>
+        <v>0.8533562287292774</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8610243042658196</v>
+        <v>0.9707475605441453</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6583787484375496</v>
+        <v>0.7085704256221388</v>
       </c>
       <c r="J2" t="n">
-        <v>1.1260431086146465</v>
+        <v>1.3299324840928923</v>
       </c>
     </row>
   </sheetData>
@@ -423,28 +423,28 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001256794488496452</v>
+        <v>0.07518886092817809</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.06843409582139569</v>
+        <v>0.0025918968471287662</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0709476847983886</v>
+        <v>0.1477858250092274</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03555657668872048</v>
+        <v>0.03703926738829047</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9718035805028898</v>
+        <v>0.04235887714855526</v>
       </c>
       <c r="H2" t="n">
-        <v>1.0012575845856515</v>
+        <v>1.0780877403102749</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9338550030224425</v>
+        <v>1.0025952587156732</v>
       </c>
       <c r="J2" t="n">
-        <v>1.073525062719186</v>
+        <v>1.1592645842911617</v>
       </c>
     </row>
   </sheetData>
@@ -495,28 +495,28 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3886014068137135</v>
+        <v>0.6070811047123411</v>
       </c>
       <c r="D2" t="n">
-        <v>0.20365214618346125</v>
+        <v>0.3833182228372567</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5735506674439658</v>
+        <v>0.8308439865874255</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09436186766849605</v>
+        <v>0.11416473565055327</v>
       </c>
       <c r="G2" t="n">
-        <v>3.818368616903005E-5</v>
+        <v>1.0515144606813368E-7</v>
       </c>
       <c r="H2" t="n">
-        <v>1.4749165424685073</v>
+        <v>1.8350672048132772</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2258716551471494</v>
+        <v>1.4671448347824898</v>
       </c>
       <c r="J2" t="n">
-        <v>1.7745567393726316</v>
+        <v>2.2952550875322784</v>
       </c>
     </row>
   </sheetData>
